--- a/playlists_04_A.xlsx
+++ b/playlists_04_A.xlsx
@@ -19,7 +19,7 @@
     <t>5YFS41yoX0YuFY39fq21oN</t>
   </si>
   <si>
-    <t>electro house 2026</t>
+    <t>electro</t>
   </si>
   <si>
     <t>6HqTlMOvZPVSGaRrCFkBLV</t>
@@ -55,151 +55,151 @@
     <t>0NGAZxHanS9e0iNHpR8f2W</t>
   </si>
   <si>
+    <t>eletro</t>
+  </si>
+  <si>
+    <t>33uRcSdNVZijCXq6qQnpuU</t>
+  </si>
+  <si>
+    <t>tiesto</t>
+  </si>
+  <si>
+    <t>2o5jDhtHVPhrJdv3cEQ99Z</t>
+  </si>
+  <si>
+    <t>boris brejcha</t>
+  </si>
+  <si>
+    <t>24abT5NjGCIyuT0ivqYoBl</t>
+  </si>
+  <si>
+    <t>calvin harris</t>
+  </si>
+  <si>
+    <t>7CajNmpbOovFoOoasH2HaY</t>
+  </si>
+  <si>
+    <t>victor lou</t>
+  </si>
+  <si>
+    <t>063wYkWkHrq5L5YWdrqjEt</t>
+  </si>
+  <si>
+    <t>4cdyqaBREB68H77QKCrKP1</t>
+  </si>
+  <si>
+    <t>5mcxg1rIaDA7hjzydZNSVk</t>
+  </si>
+  <si>
+    <t>martin garrix</t>
+  </si>
+  <si>
+    <t>60d24wfXkVzDSfLS6hyCjZ</t>
+  </si>
+  <si>
+    <t>anyma</t>
+  </si>
+  <si>
+    <t>4iBwchw0U0GZv5RfVYSMxN</t>
+  </si>
+  <si>
+    <t>acade</t>
+  </si>
+  <si>
+    <t>ilu</t>
+  </si>
+  <si>
+    <t>41zSqgoN5LIChzyMFP5M9M</t>
+  </si>
+  <si>
+    <t>dance 2026</t>
+  </si>
+  <si>
+    <t>4gHf3sODPo6qXPGnsuPU26</t>
+  </si>
+  <si>
+    <t>miss monique</t>
+  </si>
+  <si>
+    <t>29TpNOsTNYbLb6Xa10H0PR</t>
+  </si>
+  <si>
+    <t>dub</t>
+  </si>
+  <si>
+    <t>dubdogz 2026</t>
+  </si>
+  <si>
+    <t>academi</t>
+  </si>
+  <si>
+    <t>boris</t>
+  </si>
+  <si>
+    <t>6GYMqO7rTioPxDYkyA6pFS</t>
+  </si>
+  <si>
+    <t>fatsync</t>
+  </si>
+  <si>
+    <t>6H11mqvcME7dP66oQ9Nf8U</t>
+  </si>
+  <si>
+    <t>academia</t>
+  </si>
+  <si>
+    <t>28vvQFdeLvoSwwjQLyydyu</t>
+  </si>
+  <si>
+    <t>eletronica</t>
+  </si>
+  <si>
+    <t>7zQ9BS4fMLYFbybqv6ckFj</t>
+  </si>
+  <si>
+    <t>ele</t>
+  </si>
+  <si>
+    <t>2gNghi3pTCSp1XQTIxacsH</t>
+  </si>
+  <si>
+    <t>academia treino</t>
+  </si>
+  <si>
+    <t>aca</t>
+  </si>
+  <si>
+    <t>lost</t>
+  </si>
+  <si>
+    <t>1gp8CERx65hpt4td2dYF8V</t>
+  </si>
+  <si>
+    <t>7xuujsdt7kn1e9gKjttt4g</t>
+  </si>
+  <si>
+    <t>1qdA510qpITub4cMBwrHJ1</t>
+  </si>
+  <si>
+    <t>vintage</t>
+  </si>
+  <si>
+    <t>2QQhs96ItzFky97ewPYUtd</t>
+  </si>
+  <si>
+    <t>electro house</t>
+  </si>
+  <si>
+    <t>acad</t>
+  </si>
+  <si>
+    <t>treino</t>
+  </si>
+  <si>
+    <t>0XZEUrtvGcOwlvB5LVLhca</t>
+  </si>
+  <si>
     <t>eletronico</t>
-  </si>
-  <si>
-    <t>33uRcSdNVZijCXq6qQnpuU</t>
-  </si>
-  <si>
-    <t>tiesto</t>
-  </si>
-  <si>
-    <t>2o5jDhtHVPhrJdv3cEQ99Z</t>
-  </si>
-  <si>
-    <t>dance 2026 as melhores</t>
-  </si>
-  <si>
-    <t>4gHf3sODPo6qXPGnsuPU26</t>
-  </si>
-  <si>
-    <t>calvin harris</t>
-  </si>
-  <si>
-    <t>7CajNmpbOovFoOoasH2HaY</t>
-  </si>
-  <si>
-    <t>electro house</t>
-  </si>
-  <si>
-    <t>victor lou</t>
-  </si>
-  <si>
-    <t>063wYkWkHrq5L5YWdrqjEt</t>
-  </si>
-  <si>
-    <t>4cdyqaBREB68H77QKCrKP1</t>
-  </si>
-  <si>
-    <t>5mcxg1rIaDA7hjzydZNSVk</t>
-  </si>
-  <si>
-    <t>boris brejcha</t>
-  </si>
-  <si>
-    <t>6caPJFLv1wesmM7gwK1ACy</t>
-  </si>
-  <si>
-    <t>boris brejcha 2026</t>
-  </si>
-  <si>
-    <t>24abT5NjGCIyuT0ivqYoBl</t>
-  </si>
-  <si>
-    <t>anyma</t>
-  </si>
-  <si>
-    <t>4iBwchw0U0GZv5RfVYSMxN</t>
-  </si>
-  <si>
-    <t>acade</t>
-  </si>
-  <si>
-    <t>ilu</t>
-  </si>
-  <si>
-    <t>41zSqgoN5LIChzyMFP5M9M</t>
-  </si>
-  <si>
-    <t>miss monique</t>
-  </si>
-  <si>
-    <t>29TpNOsTNYbLb6Xa10H0PR</t>
-  </si>
-  <si>
-    <t>dub</t>
-  </si>
-  <si>
-    <t>dubdogz 2026</t>
-  </si>
-  <si>
-    <t>academi</t>
-  </si>
-  <si>
-    <t>boris</t>
-  </si>
-  <si>
-    <t>eletro</t>
-  </si>
-  <si>
-    <t>6GYMqO7rTioPxDYkyA6pFS</t>
-  </si>
-  <si>
-    <t>fatsync</t>
-  </si>
-  <si>
-    <t>6H11mqvcME7dP66oQ9Nf8U</t>
-  </si>
-  <si>
-    <t>academia</t>
-  </si>
-  <si>
-    <t>28vvQFdeLvoSwwjQLyydyu</t>
-  </si>
-  <si>
-    <t>eletronica</t>
-  </si>
-  <si>
-    <t>7zQ9BS4fMLYFbybqv6ckFj</t>
-  </si>
-  <si>
-    <t>ele</t>
-  </si>
-  <si>
-    <t>2gNghi3pTCSp1XQTIxacsH</t>
-  </si>
-  <si>
-    <t>academia treino</t>
-  </si>
-  <si>
-    <t>aca</t>
-  </si>
-  <si>
-    <t>lost</t>
-  </si>
-  <si>
-    <t>1gp8CERx65hpt4td2dYF8V</t>
-  </si>
-  <si>
-    <t>7xuujsdt7kn1e9gKjttt4g</t>
-  </si>
-  <si>
-    <t>1qdA510qpITub4cMBwrHJ1</t>
-  </si>
-  <si>
-    <t>vintage</t>
-  </si>
-  <si>
-    <t>2QQhs96ItzFky97ewPYUtd</t>
-  </si>
-  <si>
-    <t>acad</t>
-  </si>
-  <si>
-    <t>treino</t>
-  </si>
-  <si>
-    <t>0XZEUrtvGcOwlvB5LVLhca</t>
   </si>
   <si>
     <t>corrida</t>
@@ -587,19 +587,19 @@
         <v>21</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" ht="36.0" customHeight="1">
       <c r="C7" s="6"/>
       <c r="D7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>6</v>
@@ -613,29 +613,29 @@
         <v>10</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H8" s="5"/>
     </row>
     <row r="9" ht="36.0" customHeight="1">
       <c r="C9" s="6"/>
       <c r="D9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" ht="36.0" customHeight="1">
@@ -659,7 +659,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>10</v>
@@ -672,10 +672,10 @@
     <row r="12" ht="36.0" customHeight="1">
       <c r="C12" s="6"/>
       <c r="D12" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>2</v>
@@ -693,7 +693,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>7</v>
@@ -708,10 +708,10 @@
         <v>9</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H14" s="5"/>
     </row>
@@ -724,25 +724,25 @@
         <v>17</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" ht="36.0" customHeight="1">
       <c r="C16" s="6"/>
       <c r="D16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" ht="36.0" customHeight="1">
@@ -750,16 +750,16 @@
       <c r="B17" s="3"/>
       <c r="C17" s="6"/>
       <c r="D17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="G17" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H17" s="5"/>
     </row>
@@ -774,7 +774,7 @@
         <v>9</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>7</v>
@@ -794,7 +794,7 @@
         <v>10</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H19" s="5"/>
     </row>
@@ -820,16 +820,16 @@
       <c r="B21" s="3"/>
       <c r="C21" s="6"/>
       <c r="D21" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" ht="36.0" customHeight="1">
@@ -838,7 +838,7 @@
         <v>10</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>10</v>
@@ -857,10 +857,10 @@
         <v>9</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H23" s="5"/>
     </row>
@@ -873,10 +873,10 @@
         <v>13</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" ht="36.0" customHeight="1">
@@ -913,10 +913,10 @@
     <row r="27" ht="36.0" customHeight="1">
       <c r="C27" s="6"/>
       <c r="D27" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>2</v>
@@ -928,16 +928,16 @@
     <row r="28" ht="36.0" customHeight="1">
       <c r="C28" s="6"/>
       <c r="D28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F28" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H28" s="5"/>
     </row>
@@ -959,13 +959,13 @@
     <row r="30" ht="36.0" customHeight="1">
       <c r="C30" s="6"/>
       <c r="D30" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>7</v>
@@ -980,25 +980,25 @@
         <v>17</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" ht="36.0" customHeight="1">
       <c r="C32" s="6"/>
       <c r="D32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F32" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" ht="36.0" customHeight="1">
@@ -1013,23 +1013,23 @@
         <v>12</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H33" s="5"/>
     </row>
     <row r="34" ht="36.0" customHeight="1">
       <c r="C34" s="6"/>
       <c r="D34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F34" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" ht="36.0" customHeight="1">
@@ -1038,7 +1038,7 @@
         <v>10</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>2</v>
@@ -1059,7 +1059,7 @@
         <v>10</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H36" s="5"/>
     </row>
@@ -1072,20 +1072,20 @@
         <v>13</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H37" s="5"/>
     </row>
     <row r="38" ht="36.0" customHeight="1">
       <c r="C38" s="6"/>
       <c r="D38" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>6</v>
@@ -1097,44 +1097,44 @@
     <row r="39" ht="36.0" customHeight="1">
       <c r="C39" s="6"/>
       <c r="D39" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F39" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" ht="36.0" customHeight="1">
       <c r="C40" s="6"/>
       <c r="D40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F40" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H40" s="5"/>
     </row>
     <row r="41" ht="36.0" customHeight="1">
       <c r="C41" s="6"/>
       <c r="D41" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F41" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>7</v>
@@ -1144,10 +1144,10 @@
     <row r="42" ht="36.0" customHeight="1">
       <c r="C42" s="6"/>
       <c r="D42" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>14</v>
@@ -1159,16 +1159,16 @@
     <row r="43" ht="36.0" customHeight="1">
       <c r="C43" s="6"/>
       <c r="D43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F43" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" ht="36.0" customHeight="1">
@@ -1180,10 +1180,10 @@
         <v>17</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H44" s="5"/>
     </row>
@@ -1205,16 +1205,16 @@
     <row r="46" ht="36.0" customHeight="1">
       <c r="C46" s="6"/>
       <c r="D46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F46" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H46" s="5"/>
     </row>
@@ -1242,10 +1242,10 @@
         <v>5</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H48" s="5"/>
     </row>
@@ -1255,13 +1255,13 @@
         <v>10</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" ht="36.0" customHeight="1">
@@ -1288,50 +1288,50 @@
         <v>13</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" ht="36.0" customHeight="1">
       <c r="C52" s="6"/>
       <c r="D52" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" ht="36.0" customHeight="1">
       <c r="C53" s="6"/>
       <c r="D53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F53" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H53" s="5"/>
     </row>
     <row r="54" ht="36.0" customHeight="1">
       <c r="C54" s="6"/>
       <c r="D54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>2</v>
@@ -1343,13 +1343,13 @@
     <row r="55" ht="36.0" customHeight="1">
       <c r="C55" s="6"/>
       <c r="D55" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F55" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>7</v>
@@ -1358,16 +1358,16 @@
     <row r="56" ht="36.0" customHeight="1">
       <c r="C56" s="6"/>
       <c r="D56" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H56" s="5"/>
     </row>
@@ -1395,10 +1395,10 @@
         <v>17</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H58" s="5"/>
     </row>
@@ -1426,10 +1426,10 @@
         <v>1</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" ht="36.0" customHeight="1">
@@ -1441,7 +1441,7 @@
         <v>5</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>7</v>
@@ -1459,7 +1459,7 @@
         <v>12</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H62" s="5"/>
     </row>
@@ -1472,10 +1472,10 @@
         <v>13</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H63" s="5"/>
     </row>
@@ -1497,31 +1497,31 @@
     <row r="65" ht="36.0" customHeight="1">
       <c r="C65" s="6"/>
       <c r="D65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F65" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" ht="36.0" customHeight="1">
       <c r="C66" s="6"/>
       <c r="D66" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H66" s="5"/>
     </row>
@@ -1531,10 +1531,10 @@
         <v>10</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>7</v>
@@ -1543,16 +1543,16 @@
     <row r="68" ht="36.0" customHeight="1">
       <c r="C68" s="6"/>
       <c r="D68" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E68" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G68" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>47</v>
       </c>
       <c r="H68" s="5"/>
     </row>
@@ -1565,10 +1565,10 @@
         <v>13</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" ht="36.0" customHeight="1">
@@ -1577,7 +1577,7 @@
         <v>10</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     <row r="71" ht="36.0" customHeight="1">
       <c r="C71" s="6"/>
       <c r="D71" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>14</v>
@@ -1611,10 +1611,10 @@
         <v>13</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H72" s="5"/>
     </row>
@@ -1642,41 +1642,41 @@
         <v>17</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H74" s="5"/>
     </row>
     <row r="75" ht="36.0" customHeight="1">
       <c r="C75" s="6"/>
       <c r="D75" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E75" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F75" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" ht="36.0" customHeight="1">
       <c r="C76" s="6"/>
       <c r="D76" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>12</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H76" s="5"/>
     </row>
@@ -1704,10 +1704,10 @@
         <v>5</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" ht="36.0" customHeight="1">
@@ -1719,26 +1719,26 @@
         <v>13</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H79" s="5"/>
     </row>
     <row r="80" ht="36.0" customHeight="1">
       <c r="C80" s="6"/>
       <c r="D80" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H80" s="5"/>
     </row>
@@ -1748,10 +1748,10 @@
         <v>10</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>7</v>
@@ -1790,16 +1790,16 @@
     <row r="84" ht="36.0" customHeight="1">
       <c r="C84" s="6"/>
       <c r="D84" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" ht="36.0" customHeight="1">
@@ -1811,23 +1811,23 @@
         <v>21</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H85" s="5"/>
     </row>
     <row r="86" ht="36.0" customHeight="1">
       <c r="C86" s="6"/>
       <c r="D86" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>3</v>
@@ -1836,16 +1836,16 @@
     <row r="87" ht="36.0" customHeight="1">
       <c r="C87" s="6"/>
       <c r="D87" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F87" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H87" s="5"/>
     </row>
@@ -1858,19 +1858,19 @@
         <v>13</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="89" ht="36.0" customHeight="1">
       <c r="C89" s="6"/>
       <c r="D89" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>14</v>
@@ -1888,25 +1888,25 @@
         <v>17</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" ht="36.0" customHeight="1">
       <c r="C91" s="6"/>
       <c r="D91" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E91" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F91" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H91" s="5"/>
     </row>
@@ -1922,7 +1922,7 @@
         <v>12</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H92" s="5"/>
     </row>
@@ -1935,7 +1935,7 @@
         <v>5</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>7</v>
@@ -1944,16 +1944,16 @@
     <row r="94" ht="36.0" customHeight="1">
       <c r="C94" s="6"/>
       <c r="D94" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F94" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" ht="36.0" customHeight="1">
@@ -1980,39 +1980,39 @@
         <v>13</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H96" s="5"/>
     </row>
     <row r="97" ht="36.0" customHeight="1">
       <c r="C97" s="6"/>
       <c r="D97" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H97" s="5"/>
     </row>
     <row r="98" ht="36.0" customHeight="1">
       <c r="C98" s="6"/>
       <c r="D98" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E98" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E98" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F98" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>3</v>
@@ -2021,48 +2021,48 @@
     <row r="99" ht="36.0" customHeight="1">
       <c r="C99" s="6"/>
       <c r="D99" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F99" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H99" s="5"/>
     </row>
     <row r="100" ht="36.0" customHeight="1">
       <c r="C100" s="6"/>
       <c r="D100" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H100" s="5"/>
     </row>
     <row r="101" ht="36.0" customHeight="1">
       <c r="C101" s="6"/>
       <c r="D101" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F101" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" ht="36.0" customHeight="1">
@@ -2074,10 +2074,10 @@
         <v>21</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H102" s="5"/>
     </row>
@@ -2090,10 +2090,10 @@
         <v>17</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" ht="36.0" customHeight="1">
@@ -2105,7 +2105,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>7</v>
@@ -2114,13 +2114,13 @@
     <row r="105" ht="36.0" customHeight="1">
       <c r="C105" s="6"/>
       <c r="D105" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F105" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>3</v>
@@ -2135,26 +2135,26 @@
         <v>1</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H106" s="5"/>
     </row>
     <row r="107" ht="36.0" customHeight="1">
       <c r="C107" s="6"/>
       <c r="D107" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F107" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" ht="36.0" customHeight="1">
@@ -2163,13 +2163,13 @@
         <v>10</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="109" ht="36.0" customHeight="1">
@@ -2181,7 +2181,7 @@
         <v>9</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G109" s="5" t="s">
         <v>7</v>
@@ -2206,95 +2206,95 @@
     <row r="111" ht="36.0" customHeight="1">
       <c r="C111" s="6"/>
       <c r="D111" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H111" s="5"/>
     </row>
     <row r="112" ht="36.0" customHeight="1">
       <c r="C112" s="6"/>
       <c r="D112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E112" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F112" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" ht="36.0" customHeight="1">
       <c r="C113" s="6"/>
       <c r="D113" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E113" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E113" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F113" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H113" s="5"/>
     </row>
     <row r="114" ht="36.0" customHeight="1">
       <c r="C114" s="6"/>
       <c r="D114" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E114" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E114" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F114" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H114" s="5"/>
     </row>
     <row r="115" ht="36.0" customHeight="1">
       <c r="C115" s="6"/>
       <c r="D115" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H115" s="5"/>
     </row>
     <row r="116" ht="36.0" customHeight="1">
       <c r="C116" s="6"/>
       <c r="D116" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F116" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" ht="36.0" customHeight="1">
@@ -2321,10 +2321,10 @@
         <v>1</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H118" s="5"/>
     </row>
@@ -2353,10 +2353,10 @@
         <v>5</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H120" s="5"/>
     </row>
@@ -2384,10 +2384,10 @@
         <v>13</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H122" s="5"/>
     </row>
@@ -2400,7 +2400,7 @@
         <v>17</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>3</v>
@@ -2415,26 +2415,26 @@
         <v>21</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H124" s="5"/>
     </row>
     <row r="125" ht="36.0" customHeight="1">
       <c r="C125" s="6"/>
       <c r="D125" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" ht="36.0" customHeight="1">
@@ -2443,29 +2443,29 @@
         <v>10</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>12</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H126" s="5"/>
     </row>
     <row r="127" ht="36.0" customHeight="1">
       <c r="C127" s="6"/>
       <c r="D127" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" ht="36.0" customHeight="1">
@@ -2477,10 +2477,10 @@
         <v>13</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H128" s="5"/>
     </row>
@@ -2490,7 +2490,7 @@
         <v>10</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F129" s="4" t="s">
         <v>6</v>
@@ -2502,16 +2502,16 @@
     <row r="130" ht="36.0" customHeight="1">
       <c r="C130" s="6"/>
       <c r="D130" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H130" s="5"/>
     </row>
@@ -2539,10 +2539,10 @@
         <v>9</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H132" s="5"/>
     </row>
@@ -2564,32 +2564,32 @@
     <row r="134" ht="36.0" customHeight="1">
       <c r="C134" s="6"/>
       <c r="D134" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E134" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F134" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H134" s="5"/>
     </row>
     <row r="135" ht="36.0" customHeight="1">
       <c r="C135" s="6"/>
       <c r="D135" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E135" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E135" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F135" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" ht="36.0" customHeight="1">
@@ -2601,10 +2601,10 @@
         <v>9</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="137" ht="36.0" customHeight="1">
@@ -2616,10 +2616,10 @@
         <v>5</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H137" s="5"/>
     </row>
@@ -2632,19 +2632,19 @@
         <v>13</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" ht="36.0" customHeight="1">
       <c r="C139" s="6"/>
       <c r="D139" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>14</v>
@@ -2659,13 +2659,13 @@
         <v>10</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H140" s="5"/>
     </row>
@@ -2678,7 +2678,7 @@
         <v>9</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>7</v>
@@ -2708,10 +2708,10 @@
         <v>1</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H143" s="5"/>
     </row>
@@ -2724,20 +2724,20 @@
         <v>21</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H144" s="5"/>
     </row>
     <row r="145" ht="36.0" customHeight="1">
       <c r="C145" s="6"/>
       <c r="D145" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>14</v>
@@ -2749,16 +2749,16 @@
     <row r="146" ht="36.0" customHeight="1">
       <c r="C146" s="6"/>
       <c r="D146" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E146" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E146" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F146" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H146" s="5"/>
     </row>
@@ -2771,7 +2771,7 @@
         <v>13</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>3</v>
@@ -2780,16 +2780,16 @@
     <row r="148" ht="36.0" customHeight="1">
       <c r="C148" s="6"/>
       <c r="D148" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E148" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F148" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" ht="36.0" customHeight="1">
@@ -2811,10 +2811,10 @@
     <row r="150" ht="36.0" customHeight="1">
       <c r="C150" s="6"/>
       <c r="D150" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E150" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>14</v>
@@ -2832,10 +2832,10 @@
         <v>13</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="152" ht="36.0" customHeight="1">
@@ -2850,7 +2850,7 @@
         <v>12</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H152" s="5"/>
     </row>
@@ -2860,13 +2860,13 @@
         <v>10</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="154" ht="36.0" customHeight="1">
@@ -2878,10 +2878,10 @@
         <v>9</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H154" s="5"/>
     </row>
@@ -2903,29 +2903,29 @@
     <row r="156" ht="36.0" customHeight="1">
       <c r="C156" s="6"/>
       <c r="D156" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H156" s="5"/>
     </row>
     <row r="157" ht="36.0" customHeight="1">
       <c r="C157" s="6"/>
       <c r="D157" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E157" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E157" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F157" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>7</v>
@@ -2934,47 +2934,47 @@
     <row r="158" ht="36.0" customHeight="1">
       <c r="C158" s="6"/>
       <c r="D158" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E158" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F158" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G158" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="H158" s="5"/>
     </row>
     <row r="159" ht="36.0" customHeight="1">
       <c r="C159" s="6"/>
       <c r="D159" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E159" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F159" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" ht="36.0" customHeight="1">
       <c r="C160" s="6"/>
       <c r="D160" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" ht="36.0" customHeight="1">
@@ -2986,10 +2986,10 @@
         <v>21</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H161" s="5"/>
     </row>
@@ -3017,7 +3017,7 @@
         <v>1</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>7</v>
@@ -3026,10 +3026,10 @@
     <row r="164" ht="36.0" customHeight="1">
       <c r="C164" s="6"/>
       <c r="D164" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E164" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>14</v>
@@ -3050,7 +3050,7 @@
         <v>12</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H165" s="5"/>
     </row>
@@ -3063,10 +3063,10 @@
         <v>5</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" ht="36.0" customHeight="1">
@@ -3075,28 +3075,28 @@
         <v>10</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="168" ht="36.0" customHeight="1">
       <c r="C168" s="6"/>
       <c r="D168" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E168" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E168" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F168" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" ht="36.0" customHeight="1">
@@ -3108,7 +3108,7 @@
         <v>13</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>7</v>
@@ -3117,29 +3117,29 @@
     <row r="170" ht="36.0" customHeight="1">
       <c r="C170" s="6"/>
       <c r="D170" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F170" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E170" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="G170" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H170" s="5"/>
     </row>
     <row r="171" ht="36.0" customHeight="1">
       <c r="C171" s="6"/>
       <c r="D171" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E171" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E171" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F171" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G171" s="5" t="s">
         <v>7</v>
@@ -3149,46 +3149,46 @@
     <row r="172" ht="36.0" customHeight="1">
       <c r="C172" s="6"/>
       <c r="D172" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E172" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E172" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F172" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173" ht="36.0" customHeight="1">
       <c r="C173" s="6"/>
       <c r="D173" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="174" ht="36.0" customHeight="1">
       <c r="C174" s="6"/>
       <c r="D174" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>12</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H174" s="5"/>
     </row>
@@ -3201,10 +3201,10 @@
         <v>21</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H175" s="5"/>
     </row>
@@ -3233,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>3</v>
@@ -3248,10 +3248,10 @@
         <v>1</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H178" s="5"/>
     </row>
@@ -3264,10 +3264,10 @@
         <v>5</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="180" ht="36.0" customHeight="1">
@@ -3279,10 +3279,10 @@
         <v>9</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="181" ht="36.0" customHeight="1">
@@ -3309,10 +3309,10 @@
         <v>17</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H182" s="5"/>
     </row>
@@ -3325,7 +3325,7 @@
         <v>21</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>7</v>
@@ -3334,16 +3334,16 @@
     <row r="184" ht="36.0" customHeight="1">
       <c r="C184" s="6"/>
       <c r="D184" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E184" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E184" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F184" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="185" ht="36.0" customHeight="1">
@@ -3352,26 +3352,26 @@
         <v>10</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G185" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H185" s="5"/>
     </row>
     <row r="186" ht="36.0" customHeight="1">
       <c r="C186" s="6"/>
       <c r="D186" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>3</v>
@@ -3386,10 +3386,10 @@
         <v>13</v>
       </c>
       <c r="F187" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H187" s="5"/>
     </row>
@@ -3399,10 +3399,10 @@
         <v>10</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>7</v>
@@ -3411,16 +3411,16 @@
     <row r="189" ht="36.0" customHeight="1">
       <c r="C189" s="6"/>
       <c r="D189" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F189" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G189" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H189" s="5"/>
     </row>
@@ -3448,10 +3448,10 @@
         <v>9</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="192" ht="36.0" customHeight="1">
@@ -3463,41 +3463,41 @@
         <v>17</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="193" ht="36.0" customHeight="1">
       <c r="C193" s="6"/>
       <c r="D193" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E193" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E193" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F193" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G193" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H193" s="5"/>
     </row>
     <row r="194" ht="36.0" customHeight="1">
       <c r="C194" s="6"/>
       <c r="D194" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E194" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E194" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F194" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="195" ht="36.0" customHeight="1">
@@ -3524,7 +3524,7 @@
         <v>5</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G196" s="1" t="s">
         <v>7</v>
@@ -3539,20 +3539,20 @@
         <v>13</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H197" s="5"/>
     </row>
     <row r="198" ht="36.0" customHeight="1">
       <c r="C198" s="6"/>
       <c r="D198" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>14</v>
@@ -3567,13 +3567,13 @@
         <v>10</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H199" s="5"/>
     </row>
@@ -3586,10 +3586,10 @@
         <v>9</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="201" ht="36.0" customHeight="1">
@@ -3601,10 +3601,10 @@
         <v>13</v>
       </c>
       <c r="F201" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G201" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H201" s="5"/>
     </row>
@@ -3632,36 +3632,36 @@
         <v>21</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H203" s="5"/>
     </row>
     <row r="204" ht="36.0" customHeight="1">
       <c r="C204" s="6"/>
       <c r="D204" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G204" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H204" s="5"/>
     </row>
     <row r="205" ht="36.0" customHeight="1">
       <c r="C205" s="6"/>
       <c r="D205" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E205" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E205" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>2</v>
@@ -3679,23 +3679,23 @@
         <v>13</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G206" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H206" s="5"/>
     </row>
     <row r="207" ht="36.0" customHeight="1">
       <c r="C207" s="6"/>
       <c r="D207" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G207" s="5" t="s">
         <v>7</v>
@@ -3720,13 +3720,13 @@
     <row r="209" ht="36.0" customHeight="1">
       <c r="C209" s="6"/>
       <c r="D209" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E209" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E209" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F209" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G209" s="1" t="s">
         <v>7</v>
@@ -3735,16 +3735,16 @@
     <row r="210" ht="36.0" customHeight="1">
       <c r="C210" s="6"/>
       <c r="D210" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="211" ht="36.0" customHeight="1">
@@ -3756,10 +3756,10 @@
         <v>5</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H211" s="5"/>
     </row>
@@ -3769,10 +3769,10 @@
         <v>10</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>3</v>
@@ -3787,10 +3787,10 @@
         <v>9</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G213" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H213" s="5"/>
     </row>
@@ -3812,26 +3812,26 @@
     <row r="215" ht="36.0" customHeight="1">
       <c r="C215" s="6"/>
       <c r="D215" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G215" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H215" s="5"/>
     </row>
     <row r="216" ht="36.0" customHeight="1">
       <c r="C216" s="6"/>
       <c r="D216" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E216" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E216" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>14</v>
@@ -3843,13 +3843,13 @@
     <row r="217" ht="36.0" customHeight="1">
       <c r="C217" s="6"/>
       <c r="D217" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E217" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E217" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F217" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G217" s="1" t="s">
         <v>3</v>
@@ -3858,29 +3858,29 @@
     <row r="218" ht="36.0" customHeight="1">
       <c r="C218" s="6"/>
       <c r="D218" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E218" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E218" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F218" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H218" s="5"/>
     </row>
     <row r="219" ht="36.0" customHeight="1">
       <c r="C219" s="6"/>
       <c r="D219" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F219" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G219" s="1" t="s">
         <v>7</v>
@@ -3889,16 +3889,16 @@
     <row r="220" ht="36.0" customHeight="1">
       <c r="C220" s="6"/>
       <c r="D220" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E220" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E220" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F220" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="221" ht="36.0" customHeight="1">
@@ -3910,10 +3910,10 @@
         <v>17</v>
       </c>
       <c r="F221" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G221" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H221" s="5"/>
     </row>
@@ -3926,19 +3926,19 @@
         <v>1</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="223" ht="36.0" customHeight="1">
       <c r="C223" s="6"/>
       <c r="D223" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E223" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E223" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="F223" s="4" t="s">
         <v>6</v>
@@ -3956,10 +3956,10 @@
         <v>1</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G224" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H224" s="5"/>
     </row>
@@ -3972,7 +3972,7 @@
         <v>5</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="G225" s="1" t="s">
         <v>15</v>
@@ -3984,13 +3984,13 @@
         <v>10</v>
       </c>
       <c r="E226" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H226" s="5"/>
     </row>
@@ -4003,7 +4003,7 @@
         <v>9</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G227" s="1" t="s">
         <v>3</v>
@@ -4018,7 +4018,7 @@
         <v>13</v>
       </c>
       <c r="F228" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G228" s="1" t="s">
         <v>7</v>
@@ -4027,29 +4027,29 @@
     <row r="229" ht="36.0" customHeight="1">
       <c r="C229" s="6"/>
       <c r="D229" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E229" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F229" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E229" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F229" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="G229" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H229" s="5"/>
     </row>
     <row r="230" ht="36.0" customHeight="1">
       <c r="C230" s="6"/>
       <c r="D230" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E230" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E230" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F230" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G230" s="1" t="s">
         <v>7</v>
@@ -4058,10 +4058,10 @@
     <row r="231" ht="36.0" customHeight="1">
       <c r="C231" s="6"/>
       <c r="D231" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E231" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E231" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>18</v>
@@ -4073,32 +4073,32 @@
     <row r="232" ht="36.0" customHeight="1">
       <c r="C232" s="6"/>
       <c r="D232" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E232" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E232" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F232" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G232" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H232" s="5"/>
     </row>
     <row r="233" ht="36.0" customHeight="1">
       <c r="C233" s="6"/>
       <c r="D233" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="234" ht="36.0" customHeight="1">
@@ -4125,10 +4125,10 @@
         <v>17</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H235" s="5"/>
     </row>
@@ -4141,10 +4141,10 @@
         <v>1</v>
       </c>
       <c r="F236" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G236" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H236" s="5"/>
     </row>
@@ -4157,7 +4157,7 @@
         <v>1</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G237" s="1" t="s">
         <v>7</v>
@@ -4172,7 +4172,7 @@
         <v>5</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G238" s="1" t="s">
         <v>3</v>
@@ -4187,10 +4187,10 @@
         <v>9</v>
       </c>
       <c r="F239" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H239" s="5"/>
     </row>
@@ -4203,7 +4203,7 @@
         <v>13</v>
       </c>
       <c r="F240" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G240" s="1" t="s">
         <v>7</v>
@@ -4218,10 +4218,10 @@
         <v>17</v>
       </c>
       <c r="F241" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H241" s="5"/>
     </row>
@@ -4244,10 +4244,10 @@
     <row r="243" ht="36.0" customHeight="1">
       <c r="C243" s="6"/>
       <c r="D243" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E243" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E243" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>2</v>
@@ -4262,29 +4262,29 @@
         <v>10</v>
       </c>
       <c r="E244" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F244" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G244" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H244" s="5"/>
     </row>
     <row r="245" ht="36.0" customHeight="1">
       <c r="C245" s="6"/>
       <c r="D245" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E245" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="246" ht="36.0" customHeight="1">
@@ -4308,29 +4308,29 @@
         <v>10</v>
       </c>
       <c r="E247" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G247" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="F247" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G247" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="H247" s="5"/>
     </row>
     <row r="248" ht="36.0" customHeight="1">
       <c r="C248" s="6"/>
       <c r="D248" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="249" ht="36.0" customHeight="1">
@@ -4342,10 +4342,10 @@
         <v>13</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="250" ht="36.0" customHeight="1">
@@ -4357,10 +4357,10 @@
         <v>9</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G250" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H250" s="5"/>
     </row>
@@ -4373,7 +4373,7 @@
         <v>17</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G251" s="1" t="s">
         <v>7</v>
@@ -4382,26 +4382,26 @@
     <row r="252" ht="36.0" customHeight="1">
       <c r="C252" s="6"/>
       <c r="D252" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E252" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E252" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F252" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G252" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H252" s="5"/>
     </row>
     <row r="253" ht="36.0" customHeight="1">
       <c r="C253" s="6"/>
       <c r="D253" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E253" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>2</v>
@@ -4419,26 +4419,26 @@
         <v>9</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G254" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H254" s="5"/>
     </row>
     <row r="255" ht="36.0" customHeight="1">
       <c r="C255" s="6"/>
       <c r="D255" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="256" ht="36.0" customHeight="1">
@@ -4460,16 +4460,16 @@
     <row r="257" ht="36.0" customHeight="1">
       <c r="C257" s="6"/>
       <c r="D257" s="1" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G257" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H257" s="5"/>
     </row>
@@ -4479,13 +4479,13 @@
         <v>10</v>
       </c>
       <c r="E258" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F258" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G258" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H258" s="5"/>
     </row>
@@ -4498,10 +4498,10 @@
         <v>9</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="260" ht="36.0" customHeight="1">
@@ -4516,7 +4516,7 @@
         <v>12</v>
       </c>
       <c r="G260" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H260" s="5"/>
     </row>
@@ -4544,20 +4544,20 @@
         <v>21</v>
       </c>
       <c r="F262" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G262" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H262" s="5"/>
     </row>
     <row r="263" ht="36.0" customHeight="1">
       <c r="C263" s="6"/>
       <c r="D263" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>2</v>
@@ -4569,13 +4569,13 @@
     <row r="264" ht="36.0" customHeight="1">
       <c r="C264" s="6"/>
       <c r="D264" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E264" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E264" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F264" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G264" s="1" t="s">
         <v>7</v>
@@ -4590,25 +4590,25 @@
         <v>13</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="266" ht="36.0" customHeight="1">
       <c r="C266" s="6"/>
       <c r="D266" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E266" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E266" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F266" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="267" ht="36.0" customHeight="1">
@@ -4629,16 +4629,16 @@
     <row r="268" ht="36.0" customHeight="1">
       <c r="C268" s="6"/>
       <c r="D268" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E268" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E268" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F268" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="269" ht="36.0" customHeight="1">
@@ -4666,7 +4666,7 @@
         <v>5</v>
       </c>
       <c r="F270" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G270" s="5" t="s">
         <v>7</v>
@@ -4679,13 +4679,13 @@
         <v>10</v>
       </c>
       <c r="E271" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G271" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H271" s="5"/>
     </row>
@@ -4713,36 +4713,36 @@
         <v>13</v>
       </c>
       <c r="F273" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G273" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H273" s="5"/>
     </row>
     <row r="274" ht="36.0" customHeight="1">
       <c r="C274" s="6"/>
       <c r="D274" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E274" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F274" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G274" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="G274" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="H274" s="5"/>
     </row>
     <row r="275" ht="36.0" customHeight="1">
       <c r="C275" s="6"/>
       <c r="D275" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E275" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E275" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="F275" s="4" t="s">
         <v>6</v>
@@ -4754,13 +4754,13 @@
     <row r="276" ht="36.0" customHeight="1">
       <c r="C276" s="6"/>
       <c r="D276" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E276" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E276" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F276" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G276" s="1" t="s">
         <v>3</v>
@@ -4769,29 +4769,29 @@
     <row r="277" ht="36.0" customHeight="1">
       <c r="C277" s="6"/>
       <c r="D277" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E277" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E277" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F277" s="5" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H277" s="5"/>
     </row>
     <row r="278" ht="36.0" customHeight="1">
       <c r="C278" s="6"/>
       <c r="D278" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F278" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G278" s="1" t="s">
         <v>7</v>
@@ -4830,28 +4830,28 @@
     <row r="281" ht="36.0" customHeight="1">
       <c r="C281" s="6"/>
       <c r="D281" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E281" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E281" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F281" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="282" ht="36.0" customHeight="1">
       <c r="C282" s="6"/>
       <c r="D282" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E282" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E282" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F282" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G282" s="1" t="s">
         <v>3</v>
@@ -4866,7 +4866,7 @@
         <v>1</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G283" s="1" t="s">
         <v>7</v>
@@ -4884,7 +4884,7 @@
         <v>12</v>
       </c>
       <c r="G284" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H284" s="5"/>
     </row>
@@ -4894,7 +4894,7 @@
         <v>10</v>
       </c>
       <c r="E285" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F285" s="7" t="s">
         <v>63</v>
@@ -4929,22 +4929,22 @@
         <v>13</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="288" ht="36.0" customHeight="1">
       <c r="C288" s="6"/>
       <c r="D288" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E288" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F288" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G288" s="5" t="s">
         <v>7</v>
@@ -4954,26 +4954,26 @@
     <row r="289" ht="36.0" customHeight="1">
       <c r="C289" s="6"/>
       <c r="D289" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E289" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E289" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F289" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G289" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H289" s="5"/>
     </row>
     <row r="290" ht="36.0" customHeight="1">
       <c r="C290" s="6"/>
       <c r="D290" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E290" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="E290" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F290" s="4" t="s">
         <v>6</v>
@@ -4985,25 +4985,25 @@
     <row r="291" ht="36.0" customHeight="1">
       <c r="C291" s="6"/>
       <c r="D291" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E291" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E291" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="F291" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="292" ht="36.0" customHeight="1">
       <c r="C292" s="6"/>
       <c r="D292" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F292" s="5" t="s">
         <v>14</v>
@@ -5021,10 +5021,10 @@
         <v>21</v>
       </c>
       <c r="F293" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G293" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H293" s="5"/>
     </row>
@@ -5037,7 +5037,7 @@
         <v>17</v>
       </c>
       <c r="F294" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G294" s="1" t="s">
         <v>7</v>
@@ -5052,7 +5052,7 @@
         <v>1</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G295" s="1" t="s">
         <v>3</v>
@@ -5064,7 +5064,7 @@
         <v>10</v>
       </c>
       <c r="E296" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F296" s="5" t="s">
         <v>10</v>
@@ -5077,16 +5077,16 @@
     <row r="297" ht="36.0" customHeight="1">
       <c r="C297" s="6"/>
       <c r="D297" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E297" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E297" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="F297" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G297" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H297" s="5"/>
     </row>
@@ -5099,7 +5099,7 @@
         <v>13</v>
       </c>
       <c r="F298" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G298" s="1" t="s">
         <v>7</v>
@@ -5111,13 +5111,13 @@
         <v>10</v>
       </c>
       <c r="E299" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F299" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G299" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H299" s="5"/>
     </row>
